--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 02/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.93549</v>
+        <v>17.2247</v>
       </c>
       <c r="D2" t="n">
-        <v>17.23616</v>
+        <v>16.9619</v>
       </c>
       <c r="E2" t="n">
-        <v>17.43437</v>
+        <v>17.1736</v>
       </c>
       <c r="F2" t="n">
-        <v>44.2751</v>
+        <v>42.65627</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05222</v>
+        <v>0.05165</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84556</v>
+        <v>1.89717</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.0556</v>
+        <v>17.34199</v>
       </c>
       <c r="D3" t="n">
-        <v>17.02638</v>
+        <v>17.02217</v>
       </c>
       <c r="E3" t="n">
-        <v>17.33994</v>
+        <v>17.05515</v>
       </c>
       <c r="F3" t="n">
-        <v>43.0946</v>
+        <v>43.64409</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05173</v>
+        <v>0.05102</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84587</v>
+        <v>1.86903</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.13842</v>
+        <v>17.36483</v>
       </c>
       <c r="D4" t="n">
-        <v>16.9521</v>
+        <v>16.88486</v>
       </c>
       <c r="E4" t="n">
-        <v>17.53002</v>
+        <v>17.1263</v>
       </c>
       <c r="F4" t="n">
-        <v>43.8224</v>
+        <v>44.11873</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05265</v>
+        <v>0.05198</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8972</v>
+        <v>1.86354</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.13189</v>
+        <v>17.20792</v>
       </c>
       <c r="D6" t="n">
-        <v>16.73386</v>
+        <v>16.19107</v>
       </c>
       <c r="E6" t="n">
-        <v>16.68876</v>
+        <v>17.03833</v>
       </c>
       <c r="F6" t="n">
-        <v>22.57637</v>
+        <v>22.30766</v>
       </c>
       <c r="G6" t="n">
-        <v>35.70983</v>
+        <v>35.63645</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.23832</v>
+        <v>17.11424</v>
       </c>
       <c r="D7" t="n">
-        <v>16.24355</v>
+        <v>16.52221</v>
       </c>
       <c r="E7" t="n">
-        <v>17.05587</v>
+        <v>16.56665</v>
       </c>
       <c r="F7" t="n">
-        <v>22.28559</v>
+        <v>22.44857</v>
       </c>
       <c r="G7" t="n">
-        <v>35.08762</v>
+        <v>35.17074</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.37551</v>
+        <v>16.99047</v>
       </c>
       <c r="D8" t="n">
-        <v>16.23307</v>
+        <v>16.57333</v>
       </c>
       <c r="E8" t="n">
-        <v>16.8259</v>
+        <v>16.82015</v>
       </c>
       <c r="F8" t="n">
-        <v>22.49289</v>
+        <v>22.98413</v>
       </c>
       <c r="G8" t="n">
-        <v>35.87104</v>
+        <v>35.70068</v>
       </c>
     </row>
   </sheetData>
